--- a/test_data/number_matching_scenarios.xlsx
+++ b/test_data/number_matching_scenarios.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10927"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rishabhbhangale/Downloads/semantics/Lenovo Qlik/test_data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74F4273E-88C0-3F4B-B10F-2754ABEA82B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -88,16 +82,16 @@
     <t>Baseline Revenue: France Overall (2026-09)</t>
   </si>
   <si>
-    <t>Overdue Opportunities ISG</t>
-  </si>
-  <si>
-    <t>7 Days Opportunities ISG</t>
-  </si>
-  <si>
-    <t>Missing PN Opportunities ISG</t>
-  </si>
-  <si>
-    <t>Pipeline Hygiene ISG</t>
+    <t>Overdue Opportunities</t>
+  </si>
+  <si>
+    <t>7 Days Opportunities</t>
+  </si>
+  <si>
+    <t>Missing PN Opportunities</t>
+  </si>
+  <si>
+    <t>Pipeline Hygiene IDG</t>
   </si>
   <si>
     <t>Revenue of Overdue Opportunities</t>
@@ -172,8 +166,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,21 +230,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -288,7 +274,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -322,7 +308,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -357,10 +342,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -533,22 +517,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="47.83203125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -580,7 +553,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -612,7 +585,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -644,7 +617,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -676,7 +649,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -708,7 +681,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -740,7 +713,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>15</v>
       </c>

--- a/test_data/number_matching_scenarios.xlsx
+++ b/test_data/number_matching_scenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rishabhbhangale/Downloads/semantics/Lenovo Qlik/test_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87AEA0C1-25B1-A940-9407-F14BFA2D7BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{060BE798-F75C-2740-AC9F-90BF07C074B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
   <si>
     <t>Test ID</t>
   </si>
@@ -37,9 +37,6 @@
     <t>Measure Name</t>
   </si>
   <si>
-    <t>Calendar Filter</t>
-  </si>
-  <si>
     <t>GEO Filter</t>
   </si>
   <si>
@@ -64,16 +61,13 @@
     <t>Revenue of Overdue Opportunities</t>
   </si>
   <si>
-    <t>Revenue USD @ Actual Rate</t>
-  </si>
-  <si>
-    <t>YearMonth=2026-08</t>
+    <t>Weighted Revenue USD @ Actual Rate</t>
   </si>
   <si>
     <t>GEO Level3=BENELUX, CH</t>
   </si>
   <si>
-    <t>Past Due=-1; Business Group=IDG; Open Pipe Flag=Past Open</t>
+    <t>Past Due=-1; Open Pipe Flag=Past Open</t>
   </si>
   <si>
     <t>Overdue opportunities revenue matching against facts.csv</t>
@@ -91,6 +85,9 @@
     <t>Quantity</t>
   </si>
   <si>
+    <t>Past Due=-1; Open Pipe Flag=Past Open; Business Group=IDG, ISG</t>
+  </si>
+  <si>
     <t>Overdue opportunities quantity matching against facts.csv</t>
   </si>
   <si>
@@ -106,9 +103,6 @@
     <t>Revenue of 7 Day Opportunities</t>
   </si>
   <si>
-    <t>YearMonth=2026-09</t>
-  </si>
-  <si>
     <t>GEO Level3=CZ/SK, EECA</t>
   </si>
   <si>
@@ -127,13 +121,13 @@
     <t>Missing PN Opportunities</t>
   </si>
   <si>
-    <t>Revenue of Missing PN Opportunities</t>
+    <t>Revenue of Missing PN Opportunities by Market</t>
   </si>
   <si>
     <t>GEO Level3=FRANCE, GAT</t>
   </si>
   <si>
-    <t>Missing PN=True</t>
+    <t>Missing PN=True; Business Group=SSG; Sales Stage Gate=Execute</t>
   </si>
   <si>
     <t>Missing PN opportunities revenue matching against facts.csv</t>
@@ -148,7 +142,7 @@
     <t>Quantity of 7 Day Opportunities</t>
   </si>
   <si>
-    <t>7-day opportunities quantity matching against facts.csv</t>
+    <t>PBI author bound visual to Weighted Revenue Measure (3)</t>
   </si>
   <si>
     <t>NM-006</t>
@@ -164,6 +158,9 @@
   </si>
   <si>
     <t>GEO Level3=FRANCE</t>
+  </si>
+  <si>
+    <t>Business Group=IDG</t>
   </si>
   <si>
     <t>Baseline summary revenue validation for France in Sept 2026</t>
@@ -184,10 +181,8 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -532,21 +527,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="47.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="47.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="50.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="47.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -574,200 +568,182 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2">
+        <v>0.05</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3">
+        <v>0.05</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2">
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4">
         <v>0.01</v>
       </c>
-      <c r="J2" t="s">
-        <v>18</v>
+      <c r="I4" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5">
+        <v>0.08</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6">
         <v>0.01</v>
       </c>
-      <c r="J3" t="s">
-        <v>23</v>
+      <c r="I6" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4">
-        <v>0.01</v>
-      </c>
-      <c r="J4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5">
-        <v>0.01</v>
-      </c>
-      <c r="J5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>41</v>
       </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6">
-        <v>0.01</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="B7" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="C7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>44</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
         <v>45</v>
       </c>
-      <c r="D7" t="s">
+      <c r="G7" t="s">
         <v>46</v>
       </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="H7">
+        <v>0.08</v>
+      </c>
+      <c r="I7" t="s">
         <v>47</v>
-      </c>
-      <c r="I7">
-        <v>0.01</v>
-      </c>
-      <c r="J7" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>